--- a/assets/database/Noticias.xlsx
+++ b/assets/database/Noticias.xlsx
@@ -30,10 +30,7 @@
     <t>Ya esta a la venta nuestro calendario digital para 2027. Interesados contactar con Joan</t>
   </si>
   <si>
-    <t>ultima</t>
-  </si>
-  <si>
-    <t>ejemplo</t>
+    <t>Nueva Rifa para financiar la rehabilitación de Vida</t>
   </si>
 </sst>
 </file>
@@ -411,11 +408,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
